--- a/metadata/plate_metadata/20260324_cep290_24hpf_plate01.xlsx
+++ b/metadata/plate_metadata/20260324_cep290_24hpf_plate01.xlsx
@@ -5,7 +5,7 @@
   <sheets>
     <sheet state="visible" name="notes" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="genotype" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="seqeneced" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="sequenced" sheetId="3" r:id="rId7"/>
     <sheet state="visible" name="strain" sheetId="4" r:id="rId8"/>
     <sheet state="visible" name="chem_perturbation" sheetId="5" r:id="rId9"/>
     <sheet state="visible" name="start_stage_hpf" sheetId="6" r:id="rId10"/>
